--- a/BA_tests/LFW_confusion_matrix.xlsx
+++ b/BA_tests/LFW_confusion_matrix.xlsx
@@ -5,22 +5,23 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\programming\BA_tests\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\programming\Bachelor-Thesis-AI\BA_tests\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11B9B883-C11C-4FE0-8B12-8244F252B1CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADE1585D-F848-4FB2-9B23-9B6D8DAE236A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="-15420" windowWidth="28800" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Note" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="33">
   <si>
     <t>Model</t>
   </si>
@@ -71,6 +72,66 @@
   </si>
   <si>
     <t>FaceNet</t>
+  </si>
+  <si>
+    <t>Precision (%)</t>
+  </si>
+  <si>
+    <t>Start Time</t>
+  </si>
+  <si>
+    <t>End Time</t>
+  </si>
+  <si>
+    <t>Elapsed (sec)</t>
+  </si>
+  <si>
+    <t>2025-11-09T10:21:47.276523</t>
+  </si>
+  <si>
+    <t>2025-11-09T10:33:15.972039</t>
+  </si>
+  <si>
+    <t>2025-11-09T12:34:50.966171</t>
+  </si>
+  <si>
+    <t>2025-11-09T13:34:22.608873</t>
+  </si>
+  <si>
+    <t>2025-11-09T10:47:22.534676</t>
+  </si>
+  <si>
+    <t>2025-11-09T11:59:50.065342</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>09.11.2025</t>
+  </si>
+  <si>
+    <t>F1 Score (%)</t>
+  </si>
+  <si>
+    <t>These are aliases used by different communities:
+TPR ↔ Recall ↔ Sensitivity ↔ TAR (True Accept Rate)
+Same math: TPR = TP / (TP + FN)
+TNR ↔ Specificity
+TNR = TN / (TN + FP)
+FPR ↔ FAR (False Accept Rate)
+FPR = FP / (FP + TN) = 1 − TNR
+FNR ↔ FRR (False Reject Rate)
+FNR = FN / (FN + TP) = 1 − TPR</t>
+  </si>
+  <si>
+    <t>Why keep both?
+Biometrics vs ML terminology
+Face-recognition / biometrics papers usually say FAR/FRR, TAR.
+Generic ML libraries &amp; textbooks say FPR/FNR, Recall, Specificity.
+Storing both makes the JSON immediately readable to either audience.</t>
+  </si>
+  <si>
+    <t>08.11.2025</t>
   </si>
 </sst>
 </file>
@@ -129,12 +190,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -439,261 +504,548 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:S11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="5.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="5" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="4" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="Q1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="2">
+      <c r="D2" s="2">
         <v>6000</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E2" s="2">
         <v>0.2551867663860321</v>
       </c>
-      <c r="E2" s="2">
+      <c r="F2" s="2">
         <v>98</v>
       </c>
-      <c r="F2" s="2">
+      <c r="G2" s="2">
         <v>96.899999999999991</v>
       </c>
-      <c r="G2" s="2">
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2">
         <v>99.1</v>
       </c>
-      <c r="H2" s="2">
+      <c r="K2" s="2">
         <v>0.9000000000000008</v>
       </c>
-      <c r="I2" s="2">
+      <c r="L2" s="2">
         <v>3.1000000000000032</v>
       </c>
-      <c r="J2" s="2">
+      <c r="M2" s="2">
         <v>2907</v>
       </c>
-      <c r="K2" s="2">
+      <c r="N2" s="2">
         <v>2973</v>
       </c>
-      <c r="L2" s="2">
+      <c r="O2" s="2">
         <v>27</v>
       </c>
-      <c r="M2" s="2">
+      <c r="P2" s="2">
         <v>93</v>
       </c>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="2">
+        <v>6000</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.2551867663860321</v>
+      </c>
+      <c r="F3" s="2">
+        <v>98</v>
+      </c>
+      <c r="G3" s="2">
+        <v>96.899999999999991</v>
+      </c>
+      <c r="H3" s="2">
+        <v>99.079754601226995</v>
+      </c>
+      <c r="I3" s="2">
+        <v>97.977755308392304</v>
+      </c>
+      <c r="J3" s="2">
+        <v>99.1</v>
+      </c>
+      <c r="K3" s="2">
+        <v>0.9000000000000008</v>
+      </c>
+      <c r="L3" s="2">
+        <v>3.1000000000000032</v>
+      </c>
+      <c r="M3" s="2">
+        <v>2907</v>
+      </c>
+      <c r="N3" s="2">
+        <v>2973</v>
+      </c>
+      <c r="O3" s="2">
+        <v>27</v>
+      </c>
+      <c r="P3" s="2">
+        <v>93</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="S3" s="2">
+        <v>4347.5306659999997</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="F5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="H5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="K5" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J4" s="1" t="s">
+      <c r="M5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="N5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="O5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="P5" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="Q5" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C5">
+      <c r="D6" s="2">
         <v>6000</v>
       </c>
-      <c r="D5">
+      <c r="E6" s="2">
         <v>0.2519189715385437</v>
       </c>
-      <c r="E5">
+      <c r="F6" s="2">
         <v>88.92</v>
       </c>
-      <c r="F5">
+      <c r="G6" s="2">
         <v>87.63</v>
       </c>
-      <c r="G5">
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2">
         <v>90.2</v>
       </c>
-      <c r="H5">
+      <c r="K6" s="2">
         <v>9.8000000000000007</v>
       </c>
-      <c r="I5">
+      <c r="L6" s="2">
         <v>12.37</v>
       </c>
-      <c r="J5">
+      <c r="M6" s="2">
         <v>2629</v>
       </c>
-      <c r="K5">
+      <c r="N6" s="2">
         <v>2706</v>
       </c>
-      <c r="L5">
+      <c r="O6" s="2">
         <v>294</v>
       </c>
-      <c r="M5">
+      <c r="P6" s="2">
         <v>371</v>
       </c>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="2">
+        <v>6000</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.2519189715385437</v>
+      </c>
+      <c r="F7" s="2">
+        <v>88.916666666666671</v>
+      </c>
+      <c r="G7" s="2">
+        <v>87.633333333333326</v>
+      </c>
+      <c r="H7" s="2">
+        <v>89.941840574751964</v>
+      </c>
+      <c r="I7" s="2">
+        <v>88.772581462096895</v>
+      </c>
+      <c r="J7" s="2">
+        <v>90.2</v>
+      </c>
+      <c r="K7" s="2">
+        <v>9.7999999999999972</v>
+      </c>
+      <c r="L7" s="2">
+        <v>12.366666666666671</v>
+      </c>
+      <c r="M7" s="2">
+        <v>2629</v>
+      </c>
+      <c r="N7" s="2">
+        <v>2706</v>
+      </c>
+      <c r="O7" s="2">
+        <v>294</v>
+      </c>
+      <c r="P7" s="2">
+        <v>371</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="S7" s="2">
+        <v>3571.6427020000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="D9" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="G9" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="H9" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="K9" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J7" s="1" t="s">
+      <c r="M9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="N9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="O9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="P9" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="Q9" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B8" t="s">
+      <c r="C10" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C8">
+      <c r="D10" s="2">
         <v>6000</v>
       </c>
-      <c r="D8">
+      <c r="E10" s="2">
         <v>0.363458901643753</v>
       </c>
-      <c r="E8">
+      <c r="F10" s="2">
         <v>95.4</v>
       </c>
-      <c r="F8">
+      <c r="G10" s="2">
         <v>93.5</v>
       </c>
-      <c r="G8">
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2">
         <v>97.3</v>
       </c>
-      <c r="H8">
+      <c r="K10" s="2">
         <v>2.7</v>
       </c>
-      <c r="I8">
+      <c r="L10" s="2">
         <v>6.5</v>
       </c>
-      <c r="J8">
+      <c r="M10" s="2">
         <v>2805</v>
       </c>
-      <c r="K8">
+      <c r="N10" s="2">
         <v>2919</v>
       </c>
-      <c r="L8">
+      <c r="O10" s="2">
         <v>81</v>
       </c>
-      <c r="M8">
+      <c r="P10" s="2">
         <v>195</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="2">
+        <v>6000</v>
+      </c>
+      <c r="E11" s="2">
+        <v>0.36345890164375311</v>
+      </c>
+      <c r="F11" s="2">
+        <v>95.399999999999991</v>
+      </c>
+      <c r="G11" s="2">
+        <v>93.5</v>
+      </c>
+      <c r="H11" s="2">
+        <v>97.193347193347194</v>
+      </c>
+      <c r="I11" s="2">
+        <v>95.310907237512751</v>
+      </c>
+      <c r="J11" s="2">
+        <v>97.3</v>
+      </c>
+      <c r="K11" s="2">
+        <v>2.700000000000002</v>
+      </c>
+      <c r="L11" s="2">
+        <v>6.4999999999999947</v>
+      </c>
+      <c r="M11" s="2">
+        <v>2805</v>
+      </c>
+      <c r="N11" s="2">
+        <v>2919</v>
+      </c>
+      <c r="O11" s="2">
+        <v>81</v>
+      </c>
+      <c r="P11" s="2">
+        <v>195</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="S11" s="2">
+        <v>688.695516</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1B386EA-0113-4961-997A-319D6675CAB4}">
+  <dimension ref="B2:B3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="110.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:2" ht="195" x14ac:dyDescent="0.25">
+      <c r="B2" s="4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" ht="120" x14ac:dyDescent="0.25">
+      <c r="B3" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
